--- a/РАБОЧИЙ СТОЛ/расчет Останкино СЫРЫ/дв 07,07,26 бррсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино СЫРЫ/дв 07,07,26 бррсч ост сыр.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563B7D77-CEBF-48EC-BF0C-AFDD2A70B371}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FC544A-B1A3-49DF-8227-16360C23CFB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -298,6 +295,9 @@
   </si>
   <si>
     <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС НОВАЯ (5 кг брус) СЗМЖ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>итого</t>
   </si>
 </sst>
 </file>
@@ -913,37 +913,37 @@
         <v>15</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="AB3" s="9"/>
       <c r="AC3" s="9"/>
@@ -983,31 +983,31 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="X4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Y4" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="Z4" s="9"/>
       <c r="AA4" s="9"/>
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="C6" s="9">
         <v>241.624</v>
@@ -1200,7 +1200,7 @@
         <v>5.8540000000000001</v>
       </c>
       <c r="Z6" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA6" s="9">
         <f t="shared" ref="AA6:AA18" si="6">G6*Q6</f>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="C7" s="9">
         <v>191</v>
@@ -1295,7 +1295,7 @@
         <v>62</v>
       </c>
       <c r="Z7" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA7" s="9">
         <f t="shared" si="6"/>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="9">
         <v>228</v>
@@ -1390,7 +1390,7 @@
         <v>81</v>
       </c>
       <c r="Z8" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA8" s="9">
         <f t="shared" si="6"/>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="9">
         <v>50.47</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="9">
         <v>160</v>
@@ -1583,7 +1583,7 @@
         <v>7.6</v>
       </c>
       <c r="Z10" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA10" s="9">
         <f t="shared" si="6"/>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="9">
         <v>516</v>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="9">
         <v>180</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="9">
         <v>596</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="9">
         <v>602</v>
@@ -2013,10 +2013,10 @@
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="9">
         <v>119</v>
@@ -2078,7 +2078,7 @@
         <v>1.4</v>
       </c>
       <c r="Z15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA15" s="9">
         <f t="shared" si="6"/>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="9">
         <v>-1</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="9">
         <v>127</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="9">
         <v>109</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="9">
         <v>-7</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="9">
         <v>2629</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="9">
         <v>45</v>
@@ -2737,7 +2737,7 @@
         <v>0.4</v>
       </c>
       <c r="Z22" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="8"/>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="9">
         <v>89</v>
@@ -2830,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="Z23" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="8"/>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="9">
         <v>215</v>
@@ -2925,7 +2925,7 @@
         <v>3.6</v>
       </c>
       <c r="Z24" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA24" s="9">
         <f t="shared" si="8"/>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="9">
         <v>27</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA25" s="9">
         <f t="shared" si="8"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9">
         <v>67.125</v>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="Z26" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA26" s="9">
         <f t="shared" si="8"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9">
         <v>51.576999999999998</v>
@@ -3198,7 +3198,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="Z27" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA27" s="9">
         <f t="shared" si="8"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="10">
         <v>-2.4020000000000001</v>
@@ -3250,10 +3250,10 @@
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="9">
         <v>117</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="Z29" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA29" s="9">
         <f t="shared" ref="AA29:AA38" si="10">G29*Q29</f>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="9">
         <v>15</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA30" s="9">
         <f t="shared" si="10"/>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="9">
         <v>447</v>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="9">
         <v>191</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="9">
         <v>214</v>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="9">
         <v>551</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="9">
         <v>126</v>
@@ -3964,7 +3964,7 @@
         <v>0.2</v>
       </c>
       <c r="Z35" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA35" s="9">
         <f t="shared" si="10"/>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="9">
         <v>230</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="9">
         <v>470</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="9">
         <v>152</v>
@@ -4262,7 +4262,7 @@
         <v>31.4</v>
       </c>
       <c r="Z38" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA38" s="9">
         <f t="shared" si="10"/>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39" s="10">
         <v>-2</v>
@@ -4312,10 +4312,10 @@
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K39" s="10">
         <v>2</v>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C40" s="10">
         <v>-2</v>
@@ -4404,10 +4404,10 @@
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K40" s="10">
         <v>2</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -4494,10 +4494,10 @@
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K41" s="10">
         <v>1</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C42" s="10">
         <v>-3</v>
@@ -4586,10 +4586,10 @@
       </c>
       <c r="H42" s="10"/>
       <c r="I42" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K42" s="10">
         <v>7</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="9">
         <v>107</v>
@@ -4723,7 +4723,7 @@
         <v>3.2</v>
       </c>
       <c r="Z43" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA43" s="9">
         <f>G43*Q43</f>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C44" s="9">
         <v>66</v>
@@ -4851,10 +4851,10 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="9">
         <v>118</v>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C46" s="9">
         <v>175.744</v>
@@ -5015,7 +5015,7 @@
         <v>10.0892</v>
       </c>
       <c r="Z46" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA46" s="9">
         <f>G46*Q46</f>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C47" s="9">
         <v>137.13999999999999</v>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA47" s="9">
         <f>G47*Q47</f>
@@ -5140,10 +5140,10 @@
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="10">
         <v>-2.5099999999999998</v>
@@ -5162,10 +5162,10 @@
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K48" s="10">
         <v>3</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="49" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C49" s="9">
         <v>181.65799999999999</v>
@@ -5330,10 +5330,10 @@
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" s="9">
         <v>152.24199999999999</v>
@@ -5395,7 +5395,7 @@
         <v>6.4363999999999999</v>
       </c>
       <c r="Z50" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA50" s="9">
         <f t="shared" si="17"/>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="51" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51" s="9">
         <v>711</v>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="52" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C52" s="9">
         <v>16</v>
@@ -5620,10 +5620,10 @@
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53" s="9">
         <v>143</v>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" s="9">
         <v>128</v>
@@ -5778,7 +5778,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="Z54" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA54" s="9">
         <f t="shared" si="17"/>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="55" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="9">
         <v>99.513000000000005</v>
@@ -5873,7 +5873,7 @@
         <v>2.7692000000000001</v>
       </c>
       <c r="Z55" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA55" s="9">
         <f t="shared" si="17"/>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C56" s="9">
         <v>42</v>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="57" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -6014,10 +6014,10 @@
       <c r="G57" s="6"/>
       <c r="H57" s="9"/>
       <c r="I57" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K57" s="9">
         <v>12</v>
@@ -6089,10 +6089,10 @@
     </row>
     <row r="58" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58" s="9">
         <v>56.154000000000003</v>
